--- a/outputs/pca_eigenvalues.xlsx
+++ b/outputs/pca_eigenvalues.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>eigenvalue</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Dim.11</t>
-  </si>
-  <si>
-    <t>Dim.12</t>
   </si>
 </sst>
 </file>
@@ -121,13 +118,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2.8454225276239304</v>
+        <v>3.3364811003175827</v>
       </c>
       <c r="C2" t="n">
-        <v>23.71185439686604</v>
+        <v>30.331646366523426</v>
       </c>
       <c r="D2" t="n">
-        <v>23.71185439686604</v>
+        <v>30.331646366523426</v>
       </c>
     </row>
     <row r="3">
@@ -135,13 +132,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1.6420954953155376</v>
+        <v>1.80729587101082</v>
       </c>
       <c r="C3" t="n">
-        <v>13.684129127629454</v>
+        <v>16.429962463734697</v>
       </c>
       <c r="D3" t="n">
-        <v>37.39598352449549</v>
+        <v>46.761608830258126</v>
       </c>
     </row>
     <row r="4">
@@ -149,13 +146,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>1.1854119201225366</v>
+        <v>1.6250213074314206</v>
       </c>
       <c r="C4" t="n">
-        <v>9.878432667687786</v>
+        <v>14.772920976649251</v>
       </c>
       <c r="D4" t="n">
-        <v>47.27441619218328</v>
+        <v>61.53452980690737</v>
       </c>
     </row>
     <row r="5">
@@ -163,13 +160,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>1.0849666600110854</v>
+        <v>1.129779218181733</v>
       </c>
       <c r="C5" t="n">
-        <v>9.041388833425694</v>
+        <v>10.270720165288463</v>
       </c>
       <c r="D5" t="n">
-        <v>56.315805025608974</v>
+        <v>71.80524997219584</v>
       </c>
     </row>
     <row r="6">
@@ -177,13 +174,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9951563606580398</v>
+        <v>0.9997776147891921</v>
       </c>
       <c r="C6" t="n">
-        <v>8.292969672150315</v>
+        <v>9.08888740717446</v>
       </c>
       <c r="D6" t="n">
-        <v>64.60877469775929</v>
+        <v>80.89413737937029</v>
       </c>
     </row>
     <row r="7">
@@ -191,13 +188,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9152231167799878</v>
+        <v>0.8921788156657254</v>
       </c>
       <c r="C7" t="n">
-        <v>7.626859306499884</v>
+        <v>8.110716506052036</v>
       </c>
       <c r="D7" t="n">
-        <v>72.23563400425917</v>
+        <v>89.00485388542234</v>
       </c>
     </row>
     <row r="8">
@@ -205,13 +202,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8229157301774279</v>
+        <v>0.5970565778591059</v>
       </c>
       <c r="C8" t="n">
-        <v>6.857631084811886</v>
+        <v>5.427787071446408</v>
       </c>
       <c r="D8" t="n">
-        <v>79.09326508907105</v>
+        <v>94.43264095686874</v>
       </c>
     </row>
     <row r="9">
@@ -219,13 +216,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7286218727504302</v>
+        <v>0.4899562051443638</v>
       </c>
       <c r="C9" t="n">
-        <v>6.071848939586907</v>
+        <v>4.454147319494208</v>
       </c>
       <c r="D9" t="n">
-        <v>85.16511402865797</v>
+        <v>98.88678827636295</v>
       </c>
     </row>
     <row r="10">
@@ -233,13 +230,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7042833617612145</v>
+        <v>0.1176862544084263</v>
       </c>
       <c r="C10" t="n">
-        <v>5.869028014676776</v>
+        <v>1.0698750400766008</v>
       </c>
       <c r="D10" t="n">
-        <v>91.03414204333474</v>
+        <v>99.95666331643955</v>
       </c>
     </row>
     <row r="11">
@@ -247,13 +244,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4906219341209859</v>
+        <v>0.004767035191649504</v>
       </c>
       <c r="C11" t="n">
-        <v>4.0885161176748746</v>
+        <v>0.04333668356044996</v>
       </c>
       <c r="D11" t="n">
-        <v>95.12265816100962</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="12">
@@ -261,26 +258,12 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3958043500372185</v>
+        <v>1.9566654738234406E-31</v>
       </c>
       <c r="C12" t="n">
-        <v>3.2983695836434808</v>
+        <v>1.7787867943849426E-30</v>
       </c>
       <c r="D12" t="n">
-        <v>98.4210277446531</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.18947667064162865</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.5789722553469023</v>
-      </c>
-      <c r="D13" t="n">
         <v>100.0</v>
       </c>
     </row>
